--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="496">
   <si>
     <t>Filename</t>
   </si>
@@ -808,706 +808,700 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9957,0.0008,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9987,0.0000,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.0031,0.0001,0.0001,0.9993</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.0049,0.0003,0.0000,0.9991</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.4263,0.0005,0.6784,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0002,0.9972,0.0004</t>
+  </si>
+  <si>
+    <t>0.4662,0.0020,0.5717,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.0011,0.9926,0.0004</t>
+  </si>
+  <si>
+    <t>0.9748,0.0010,0.0207,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0038,0.9904,0.0039,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.9992,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0111,0.0007,0.9848,0.0008</t>
+  </si>
+  <si>
+    <t>0.8451,0.0011,0.1998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.0000,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.0000,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9655,0.0300,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9816,0.0035,0.0078,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0008,0.9997,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.9976,0.0209,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9766,0.0003,0.0266,0.0002</t>
+  </si>
+  <si>
+    <t>0.2033,0.7951,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.0006,0.9988,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.7010,0.5833,0.0191</t>
+  </si>
+  <si>
+    <t>0.0050,0.0001,0.9917,0.0008</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0057,0.0001,0.9927,0.0005</t>
+  </si>
+  <si>
+    <t>0.0610,0.0139,0.9279,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0394,0.9973,0.0008</t>
+  </si>
+  <si>
+    <t>0.0013,0.1783,0.0000,0.9681</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0043,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0019,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.0176,0.9941,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0009,0.9960,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0018,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0012,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0003,0.0003</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9983,0.0007,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9715,0.0008,0.0214,0.0001</t>
-  </si>
-  <si>
-    <t>0.0069,0.0004,0.9934,0.0003</t>
-  </si>
-  <si>
-    <t>0.2653,0.0030,0.7357,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9989,0.0007</t>
-  </si>
-  <si>
-    <t>0.8763,0.0010,0.1457,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.9962,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.9989,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9218,0.0011,0.0667,0.0005</t>
-  </si>
-  <si>
-    <t>0.1674,0.0031,0.8192,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.0005,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.0001,0.9960,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0484,0.9417,0.0030,0.0014</t>
-  </si>
-  <si>
-    <t>0.9051,0.0189,0.0325,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,1.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0062,0.9834,0.0151,0.0005</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9311,0.0014,0.0791,0.0005</t>
-  </si>
-  <si>
-    <t>0.2223,0.8175,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.9992,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0233,0.6110,0.1948,0.0571</t>
-  </si>
-  <si>
-    <t>0.0069,0.0011,0.9820,0.0028</t>
-  </si>
-  <si>
-    <t>0.0005,0.0026,0.9979,0.0002</t>
-  </si>
-  <si>
-    <t>0.0108,0.0000,0.9908,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.8766,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0030,0.9943,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.0456,0.0003,0.9951</t>
-  </si>
-  <si>
-    <t>0.0004,0.9990,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0022,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0053,0.9981,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0662,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9988,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0011,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0007,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0137</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9924,0.0031,0.0013,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9639,0.9970,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0016,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0061,0.1154,0.9498,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9964,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0005</t>
-  </si>
-  <si>
-    <t>0.0018,0.9971,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9705,0.0006,0.0355,0.0001</t>
-  </si>
-  <si>
-    <t>0.9840,0.0034,0.0047,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0010,0.9994,0.0022</t>
-  </si>
-  <si>
-    <t>0.0000,0.9967,0.9964,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9955,0.9905,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.9940,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0129,0.9979</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
+    <t>0.0000,0.0023,1.0000,0.0057</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0009,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.9920,0.9962,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0030,0.9926,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.9882,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0029,0.9956,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9936,0.0004,0.0040,0.0001</t>
+  </si>
+  <si>
+    <t>0.9645,0.0103,0.0073,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.0024,0.9983,0.0022</t>
+  </si>
+  <si>
+    <t>0.0000,0.9978,0.9776,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9928,0.9946,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9930,0.9515,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0164,0.9940</t>
+  </si>
+  <si>
+    <t>0.0000,0.0013,0.0000,1.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0014,0.0001,0.0001,0.9994</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0037,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9961,0.6331,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.9968,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9956,0.9518,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9896,0.2248,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.9865,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.8203,0.9865,0.0000</t>
+    <t>0.0004,0.0000,0.0002,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0073,0.9994</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.2127,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9632,0.8732,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9953,0.8637,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9793,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9560,0.9945,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0038,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9966,0.0030,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0002,0.0001</t>
   </si>
   <si>
     <t>0.9994,0.0002,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9952,0.0022,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9964,0.0024,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0010,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9963,0.0019,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0005,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9967,0.0020,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0010,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0001,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9958,0.0024,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0665,0.9211,0.0155,0.0002</t>
-  </si>
-  <si>
-    <t>0.7014,0.0168,0.1414,0.0020</t>
-  </si>
-  <si>
-    <t>0.0057,0.0003,0.9908,0.0017</t>
-  </si>
-  <si>
-    <t>0.7481,0.0091,0.1345,0.0022</t>
-  </si>
-  <si>
-    <t>0.0040,0.0111,0.9815,0.0016</t>
-  </si>
-  <si>
-    <t>0.0001,0.0016,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9982,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0583,0.9341,0.0058,0.0006</t>
-  </si>
-  <si>
-    <t>0.9097,0.0531,0.0065,0.0036</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0004,0.0002</t>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9962,0.0023,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9997,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.0003,0.0000,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0007,0.9975,0.0001</t>
+  </si>
+  <si>
+    <t>0.0089,0.0002,0.9939,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.9912,0.0030,0.0006</t>
+  </si>
+  <si>
+    <t>0.0007,0.9978,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2894,0.8096,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9268,0.0210,0.0108,0.0013</t>
+  </si>
+  <si>
+    <t>0.4317,0.0131,0.3182,0.0022</t>
+  </si>
+  <si>
+    <t>0.0648,0.0158,0.8633,0.0012</t>
+  </si>
+  <si>
+    <t>0.0444,0.0050,0.9496,0.0007</t>
+  </si>
+  <si>
+    <t>0.0009,0.0027,0.0010,0.9969</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.9968,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.2452,0.7511,0.0031,0.0004</t>
+  </si>
+  <si>
+    <t>0.9889,0.0056,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9887,0.9426,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9695,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0024,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0013,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.5405,0.0016,0.3970,0.0030</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.9917,0.0005,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.0220,0.0000,0.0000,0.9972</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0064,0.9989</t>
+  </si>
+  <si>
+    <t>0.0000,0.9913,0.9969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0067,0.9888,0.0015,0.0013</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.5875,0.3639,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9943,0.0002,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0418,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.9212,0.0001,0.0153,0.0191</t>
+  </si>
+  <si>
+    <t>0.9931,0.0000,0.0001,0.0055</t>
+  </si>
+  <si>
+    <t>0.4480,0.6630,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9865,0.0032,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.2120,0.7341,0.0025,0.0014</t>
+  </si>
+  <si>
+    <t>0.8912,0.0110,0.0522,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0005</t>
+  </si>
+  <si>
     <t>0.9993,0.0001,0.0002,0.0001</t>
   </si>
   <si>
+    <t>0.9996,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9940,0.0022,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0009,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.8683,0.0538,0.0246,0.0013</t>
+  </si>
+  <si>
+    <t>0.1953,0.6946,0.0311,0.0019</t>
+  </si>
+  <si>
+    <t>0.0427,0.0380,0.9607,0.0006</t>
+  </si>
+  <si>
+    <t>0.9876,0.0212,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0005,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9959,0.0011,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.8794,0.1143,0.0019,0.0014</t>
+  </si>
+  <si>
+    <t>0.0001,0.0393,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0006,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0476,0.9971,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0019,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0050,0.9908,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0014,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0058,0.0067,0.9863,0.0010</t>
+  </si>
+  <si>
+    <t>0.0192,0.0003,0.9884,0.0001</t>
+  </si>
+  <si>
+    <t>0.0181,0.0069,0.9606,0.0007</t>
+  </si>
+  <si>
+    <t>0.2198,0.0281,0.5142,0.0017</t>
+  </si>
+  <si>
+    <t>0.0007,0.1913,0.9784,0.0003</t>
+  </si>
+  <si>
+    <t>0.0478,0.0054,0.9340,0.0001</t>
+  </si>
+  <si>
+    <t>0.9666,0.0047,0.0040,0.0009</t>
+  </si>
+  <si>
+    <t>0.7176,0.0057,0.1709,0.0029</t>
+  </si>
+  <si>
+    <t>0.0541,0.9522,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.9990,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.7518,0.3324,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.5558,0.5044,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.1007,0.9211,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8673,0.0092,0.0741,0.0002</t>
+  </si>
+  <si>
+    <t>0.8932,0.0028,0.0408,0.0049</t>
+  </si>
+  <si>
+    <t>0.4508,0.0113,0.4822,0.0002</t>
+  </si>
+  <si>
+    <t>0.2374,0.0014,0.7776,0.0010</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.9982,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.0356,0.9930,0.0006</t>
+  </si>
+  <si>
+    <t>0.0107,0.0020,0.9870,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0055,0.2362,0.7933,0.0008</t>
+  </si>
+  <si>
+    <t>0.9960,0.0020,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0015,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0010,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0002,0.0002</t>
+  </si>
+  <si>
     <t>0.9998,0.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.9966,0.6175,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.5680,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0020,0.9942,0.0004</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1702,0.0028,0.7344,0.0102</t>
-  </si>
-  <si>
-    <t>0.0109,0.0002,0.9913,0.0003</t>
-  </si>
-  <si>
-    <t>0.7830,0.0248,0.0895,0.0012</t>
-  </si>
-  <si>
-    <t>0.0170,0.0000,0.0000,0.9981</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0029,0.9994</t>
-  </si>
-  <si>
-    <t>0.0000,0.9930,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0107,0.9847,0.0008,0.0023</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0726,0.9132,0.0029,0.0019</t>
-  </si>
-  <si>
-    <t>0.9973,0.0002,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9608,0.0001,0.0004,0.0482</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0903,0.9985,0.0002</t>
-  </si>
-  <si>
-    <t>0.9933,0.0001,0.0016,0.0022</t>
-  </si>
-  <si>
-    <t>0.9903,0.0000,0.0010,0.0030</t>
-  </si>
-  <si>
-    <t>0.6187,0.4226,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9908,0.0013,0.0048,0.0002</t>
-  </si>
-  <si>
-    <t>0.1623,0.2652,0.1574,0.0002</t>
-  </si>
-  <si>
-    <t>0.9825,0.0059,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0002,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9918,0.0013,0.0039,0.0004</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9966,0.0032,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.6429,0.2254,0.0445,0.0012</t>
-  </si>
-  <si>
-    <t>0.5297,0.4611,0.0129,0.0005</t>
-  </si>
-  <si>
-    <t>0.1557,0.1399,0.7736,0.0009</t>
-  </si>
-  <si>
-    <t>0.8561,0.1815,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9975,0.0005,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9917,0.0023,0.0025,0.0009</t>
-  </si>
-  <si>
-    <t>0.9915,0.0041,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0057,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9752,0.0060,0.0047,0.0084</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0391,0.0307,0.9198,0.0018</t>
-  </si>
-  <si>
-    <t>0.0026,0.0010,0.9964,0.0003</t>
-  </si>
-  <si>
-    <t>0.0025,0.0465,0.9887,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9996,0.0001</t>
+    <t>0.0001,0.0034,0.9995,0.0009</t>
+  </si>
+  <si>
+    <t>0.0031,0.9790,0.0304,0.0009</t>
+  </si>
+  <si>
+    <t>0.9390,0.0005,0.0380,0.0042</t>
+  </si>
+  <si>
+    <t>0.0002,0.0026,0.9990,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.1407,0.9913,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0130,0.0243,0.9513,0.0020</t>
-  </si>
-  <si>
-    <t>0.0162,0.0008,0.9864,0.0002</t>
-  </si>
-  <si>
-    <t>0.3866,0.0041,0.5531,0.0008</t>
-  </si>
-  <si>
-    <t>0.0987,0.0047,0.8778,0.0005</t>
-  </si>
-  <si>
-    <t>0.0327,0.0785,0.8176,0.0007</t>
-  </si>
-  <si>
-    <t>0.0289,0.0052,0.9613,0.0001</t>
-  </si>
-  <si>
-    <t>0.9587,0.0048,0.0062,0.0022</t>
-  </si>
-  <si>
-    <t>0.7437,0.0022,0.2135,0.0021</t>
-  </si>
-  <si>
-    <t>0.0014,0.9960,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.0015,0.9960,0.0037,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.9890,0.0033,0.0008</t>
-  </si>
-  <si>
-    <t>0.9943,0.0049,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0432,0.9672,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9800,0.0082,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9880,0.0005,0.0073,0.0000</t>
-  </si>
-  <si>
-    <t>0.9922,0.0004,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.6745,0.0037,0.3568,0.0001</t>
-  </si>
-  <si>
-    <t>0.2149,0.0014,0.8012,0.0009</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9995,0.0003</t>
-  </si>
-  <si>
-    <t>0.0036,0.0178,0.9841,0.0007</t>
-  </si>
-  <si>
-    <t>0.0035,0.0057,0.9932,0.0002</t>
-  </si>
-  <si>
-    <t>0.0021,0.0008,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0858,0.9118,0.0029</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9972,0.0008,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9979,0.0011,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0116,0.9968,0.0014</t>
-  </si>
-  <si>
-    <t>0.0068,0.9595,0.0361,0.0019</t>
-  </si>
-  <si>
-    <t>0.8955,0.0008,0.0867,0.0010</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0014,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.6479,0.9739,0.0001</t>
+    <t>0.0006,0.0001,0.9989,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0001,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0017,0.0002,0.9969,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0048,0.9955,0.0002</t>
-  </si>
-  <si>
-    <t>0.0111,0.0008,0.9790,0.0016</t>
-  </si>
-  <si>
-    <t>0.9731,0.0017,0.0143,0.0001</t>
-  </si>
-  <si>
-    <t>0.9819,0.0002,0.0189,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9899,0.0090,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9970,0.0012,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9960,0.0016,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9954,0.0031,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0017,0.9970,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0282,0.9861,0.0018</t>
-  </si>
-  <si>
-    <t>0.0211,0.0106,0.9426,0.0009</t>
-  </si>
-  <si>
-    <t>0.0025,0.0001,0.9967,0.0004</t>
-  </si>
-  <si>
-    <t>0.0735,0.0002,0.6553,0.0875</t>
-  </si>
-  <si>
-    <t>0.2921,0.0010,0.7391,0.0007</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9982,0.0008</t>
-  </si>
-  <si>
-    <t>0.9672,0.0001,0.0010,0.0323</t>
-  </si>
-  <si>
-    <t>0.0003,0.0020,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0050,0.0002,0.0000,0.9989</t>
-  </si>
-  <si>
-    <t>0.7920,0.0021,0.0001,0.1993</t>
+    <t>0.0017,0.0064,0.9948,0.0001</t>
+  </si>
+  <si>
+    <t>0.0368,0.0009,0.9439,0.0052</t>
+  </si>
+  <si>
+    <t>0.8609,0.0067,0.0849,0.0005</t>
+  </si>
+  <si>
+    <t>0.1211,0.0002,0.9084,0.0006</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9891,0.0065,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9981,0.0006,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9954,0.0028,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0039,0.0039,0.9886,0.0010</t>
+  </si>
+  <si>
+    <t>0.0017,0.0158,0.9856,0.0020</t>
+  </si>
+  <si>
+    <t>0.0008,0.0945,0.9780,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.0340,0.0001,0.9175,0.0097</t>
+  </si>
+  <si>
+    <t>0.0066,0.0004,0.9923,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.0003,0.9963,0.0008</t>
+  </si>
+  <si>
+    <t>0.8428,0.0001,0.0009,0.2475</t>
+  </si>
+  <si>
+    <t>0.0004,0.0014,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0070,0.0000,0.0000,0.9989</t>
+  </si>
+  <si>
+    <t>0.9935,0.0002,0.0001,0.0029</t>
   </si>
 </sst>
 </file>
@@ -1893,7 +1887,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1907,7 +1901,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1921,7 +1915,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1935,7 +1929,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1949,7 +1943,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1963,7 +1957,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1977,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1991,7 +1985,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2005,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2019,7 +2013,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2033,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2047,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2058,10 +2052,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2075,7 +2069,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2089,7 +2083,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2103,7 +2097,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2117,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2131,7 +2125,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2145,7 +2139,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2159,7 +2153,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2173,7 +2167,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2187,7 +2181,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2198,10 +2192,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2212,10 +2206,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2229,7 +2223,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2243,7 +2237,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2257,7 +2251,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2271,7 +2265,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2285,7 +2279,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2296,10 +2290,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2313,7 +2307,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2327,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2341,7 +2335,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2355,7 +2349,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2369,7 +2363,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2383,7 +2377,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2397,7 +2391,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2408,10 +2402,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2425,7 +2419,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2439,7 +2433,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2453,7 +2447,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2464,10 +2458,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2481,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2495,7 +2489,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2509,7 +2503,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2523,7 +2517,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2537,7 +2531,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2551,7 +2545,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2565,7 +2559,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2579,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2593,7 +2587,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2607,7 +2601,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2621,7 +2615,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2635,7 +2629,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2649,7 +2643,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2663,7 +2657,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2677,7 +2671,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2691,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2705,7 +2699,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2719,7 +2713,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>277</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2733,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2747,7 +2741,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2761,7 +2755,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2775,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2789,7 +2783,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2803,7 +2797,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2817,7 +2811,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2831,7 +2825,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>280</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2845,7 +2839,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2859,7 +2853,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2873,7 +2867,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2887,7 +2881,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2901,7 +2895,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2915,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2929,7 +2923,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2943,7 +2937,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2957,7 +2951,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2971,7 +2965,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2985,7 +2979,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2999,7 +2993,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3013,7 +3007,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3024,10 +3018,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3041,7 +3035,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3055,7 +3049,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3066,10 +3060,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3083,7 +3077,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3097,7 +3091,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3111,7 +3105,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3125,7 +3119,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3139,7 +3133,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3153,7 +3147,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3167,7 +3161,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3181,7 +3175,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3195,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3209,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3223,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3237,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3251,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3265,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>357</v>
+        <v>277</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3279,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3293,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3307,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>268</v>
+        <v>362</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3321,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>363</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3335,7 +3329,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3349,7 +3343,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3363,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3377,7 +3371,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3391,7 +3385,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>363</v>
+        <v>283</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3405,7 +3399,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3419,7 +3413,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3433,7 +3427,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3447,7 +3441,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>280</v>
+        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3461,7 +3455,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3475,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3489,7 +3483,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3500,10 +3494,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3514,10 +3508,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3531,7 +3525,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3545,7 +3539,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3559,7 +3553,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>313</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3573,7 +3567,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>280</v>
+        <v>376</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3587,7 +3581,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>309</v>
+        <v>283</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3601,7 +3595,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3615,7 +3609,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3629,7 +3623,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3643,7 +3637,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3657,7 +3651,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>377</v>
+        <v>322</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3671,7 +3665,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3685,7 +3679,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>268</v>
+        <v>382</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3699,7 +3693,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3713,7 +3707,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3727,7 +3721,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>377</v>
+        <v>277</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3741,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3755,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3769,7 +3763,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3783,7 +3777,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3797,7 +3791,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3811,7 +3805,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3825,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>387</v>
+        <v>322</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3836,10 +3830,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3853,7 +3847,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3867,7 +3861,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3881,7 +3875,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3895,7 +3889,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>338</v>
+        <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3909,7 +3903,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3923,7 +3917,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3937,7 +3931,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3951,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>274</v>
+        <v>322</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3965,7 +3959,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3979,7 +3973,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3990,10 +3984,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4007,7 +4001,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4021,7 +4015,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4035,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4049,7 +4043,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4063,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4077,7 +4071,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4088,10 +4082,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4105,7 +4099,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4119,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4130,10 +4124,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4147,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4161,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4175,7 +4169,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4189,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4203,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4217,7 +4211,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4231,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4245,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4259,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4273,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4287,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4301,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4312,10 +4306,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4329,7 +4323,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4343,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4357,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4371,7 +4365,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4385,7 +4379,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4399,7 +4393,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4413,7 +4407,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4427,7 +4421,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4441,7 +4435,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4455,7 +4449,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4469,7 +4463,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4483,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4497,7 +4491,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4511,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4525,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4539,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4553,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4567,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4581,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4595,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4609,7 +4603,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4623,7 +4617,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4637,7 +4631,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4651,7 +4645,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4662,10 +4656,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4676,10 +4670,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D201" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4693,7 +4687,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4707,7 +4701,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4721,7 +4715,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4735,7 +4729,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4746,10 +4740,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4763,7 +4757,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4777,7 +4771,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4791,7 +4785,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4805,7 +4799,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4819,7 +4813,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4833,7 +4827,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4847,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>456</v>
+        <v>362</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4861,7 +4855,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4875,7 +4869,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4889,7 +4883,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4903,7 +4897,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4917,7 +4911,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4931,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>462</v>
+        <v>385</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4945,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4959,7 +4953,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4973,7 +4967,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4987,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5001,7 +4995,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>467</v>
+        <v>437</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5015,7 +5009,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5026,10 +5020,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5043,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5057,7 +5051,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5071,7 +5065,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5085,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5099,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5113,7 +5107,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5124,10 +5118,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5141,7 +5135,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5155,7 +5149,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5169,7 +5163,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5183,7 +5177,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>480</v>
+        <v>355</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5197,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5211,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>482</v>
+        <v>277</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5225,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5253,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>485</v>
+        <v>352</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5267,7 +5261,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5281,7 +5275,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5295,7 +5289,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5309,7 +5303,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5323,7 +5317,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5337,7 +5331,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5351,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5365,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5379,7 +5373,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5393,7 +5387,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5407,7 +5401,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5421,7 +5415,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5435,7 +5429,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5449,7 +5443,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
